--- a/artfynd/A 49243-2023 artfynd.xlsx
+++ b/artfynd/A 49243-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126493422</v>
       </c>
       <c r="B2" t="n">
-        <v>91245</v>
+        <v>91504</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -768,14 +768,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>126493428</v>
       </c>
       <c r="B3" t="n">
-        <v>80119</v>
+        <v>80261</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -865,14 +869,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>126493426</v>
       </c>
       <c r="B4" t="n">
-        <v>57817</v>
+        <v>57876</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -962,14 +970,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
         <v>126493433</v>
       </c>
       <c r="B5" t="n">
-        <v>78980</v>
+        <v>79120</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1059,14 +1071,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
         <v>126493431</v>
       </c>
       <c r="B6" t="n">
-        <v>78980</v>
+        <v>79120</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1156,14 +1172,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
         <v>126493429</v>
       </c>
       <c r="B7" t="n">
-        <v>91652</v>
+        <v>91911</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1248,14 +1268,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr"/>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
         <v>126493432</v>
       </c>
       <c r="B8" t="n">
-        <v>78980</v>
+        <v>79120</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1345,7 +1369,11 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr"/>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 49243-2023 artfynd.xlsx
+++ b/artfynd/A 49243-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126493422</v>
       </c>
       <c r="B2" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>126493428</v>
       </c>
       <c r="B3" t="n">
-        <v>80261</v>
+        <v>80265</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>126493426</v>
       </c>
       <c r="B4" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>126493433</v>
       </c>
       <c r="B5" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>126493431</v>
       </c>
       <c r="B6" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>126493429</v>
       </c>
       <c r="B7" t="n">
-        <v>91911</v>
+        <v>91915</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
         <v>126493432</v>
       </c>
       <c r="B8" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 49243-2023 artfynd.xlsx
+++ b/artfynd/A 49243-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126493422</v>
       </c>
       <c r="B2" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>126493428</v>
       </c>
       <c r="B3" t="n">
-        <v>80265</v>
+        <v>80170</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>126493426</v>
       </c>
       <c r="B4" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>126493433</v>
       </c>
       <c r="B5" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>126493431</v>
       </c>
       <c r="B6" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>126493429</v>
       </c>
       <c r="B7" t="n">
-        <v>91915</v>
+        <v>91920</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
         <v>126493432</v>
       </c>
       <c r="B8" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 49243-2023 artfynd.xlsx
+++ b/artfynd/A 49243-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126493422</v>
       </c>
       <c r="B2" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>126493429</v>
       </c>
       <c r="B7" t="n">
-        <v>91928</v>
+        <v>91931</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 49243-2023 artfynd.xlsx
+++ b/artfynd/A 49243-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126493422</v>
       </c>
       <c r="B2" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>126493428</v>
       </c>
       <c r="B3" t="n">
-        <v>80175</v>
+        <v>80176</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>126493433</v>
       </c>
       <c r="B5" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>126493431</v>
       </c>
       <c r="B6" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>126493429</v>
       </c>
       <c r="B7" t="n">
-        <v>91931</v>
+        <v>91934</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
         <v>126493432</v>
       </c>
       <c r="B8" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 49243-2023 artfynd.xlsx
+++ b/artfynd/A 49243-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126493422</v>
       </c>
       <c r="B2" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>126493428</v>
       </c>
       <c r="B3" t="n">
-        <v>80176</v>
+        <v>80180</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>126493426</v>
       </c>
       <c r="B4" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>126493433</v>
       </c>
       <c r="B5" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>126493431</v>
       </c>
       <c r="B6" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>126493429</v>
       </c>
       <c r="B7" t="n">
-        <v>91934</v>
+        <v>91941</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
         <v>126493432</v>
       </c>
       <c r="B8" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 49243-2023 artfynd.xlsx
+++ b/artfynd/A 49243-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126493422</v>
       </c>
       <c r="B2" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>126493429</v>
       </c>
       <c r="B7" t="n">
-        <v>91941</v>
+        <v>91948</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 49243-2023 artfynd.xlsx
+++ b/artfynd/A 49243-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126493422</v>
       </c>
       <c r="B2" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>126493428</v>
       </c>
       <c r="B3" t="n">
-        <v>80180</v>
+        <v>80182</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>126493426</v>
       </c>
       <c r="B4" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>126493433</v>
       </c>
       <c r="B5" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>126493431</v>
       </c>
       <c r="B6" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>126493429</v>
       </c>
       <c r="B7" t="n">
-        <v>91948</v>
+        <v>91950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
         <v>126493432</v>
       </c>
       <c r="B8" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 49243-2023 artfynd.xlsx
+++ b/artfynd/A 49243-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126493422</v>
       </c>
       <c r="B2" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>126493429</v>
       </c>
       <c r="B7" t="n">
-        <v>91950</v>
+        <v>91958</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 49243-2023 artfynd.xlsx
+++ b/artfynd/A 49243-2023 artfynd.xlsx
@@ -1183,7 +1183,7 @@
         <v>126493429</v>
       </c>
       <c r="B7" t="n">
-        <v>91958</v>
+        <v>91959</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 49243-2023 artfynd.xlsx
+++ b/artfynd/A 49243-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126493422</v>
       </c>
       <c r="B2" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>126493428</v>
       </c>
       <c r="B3" t="n">
-        <v>80182</v>
+        <v>80184</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>126493433</v>
       </c>
       <c r="B5" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>126493431</v>
       </c>
       <c r="B6" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>126493429</v>
       </c>
       <c r="B7" t="n">
-        <v>91959</v>
+        <v>91962</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
         <v>126493432</v>
       </c>
       <c r="B8" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 49243-2023 artfynd.xlsx
+++ b/artfynd/A 49243-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126493422</v>
       </c>
       <c r="B2" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>126493428</v>
       </c>
       <c r="B3" t="n">
-        <v>80184</v>
+        <v>80185</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>126493433</v>
       </c>
       <c r="B5" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>126493431</v>
       </c>
       <c r="B6" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>126493429</v>
       </c>
       <c r="B7" t="n">
-        <v>91962</v>
+        <v>91964</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
         <v>126493432</v>
       </c>
       <c r="B8" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 49243-2023 artfynd.xlsx
+++ b/artfynd/A 49243-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126493422</v>
       </c>
       <c r="B2" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>126493429</v>
       </c>
       <c r="B7" t="n">
-        <v>91964</v>
+        <v>91968</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
